--- a/邀请函-名单.xlsx
+++ b/邀请函-名单.xlsx
@@ -32,7 +32,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="146" uniqueCount="146">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="148" uniqueCount="148">
   <si>
     <t>姓名</t>
   </si>
@@ -470,6 +470,12 @@
   </si>
   <si>
     <t>负琴奏潇湘水云，见你如酒水满、竹林间，高山流水遇美仙。小跳蛛来赴宴吧~</t>
+  </si>
+  <si>
+    <t>李林馨</t>
+  </si>
+  <si>
+    <t>小公主殿下，本王子的生日要到了，邀请你来我的云上王国赴宴！</t>
   </si>
 </sst>
 </file>
@@ -1614,7 +1620,7 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData">
   <sheetPr/>
-  <dimension ref="A1:B73"/>
+  <dimension ref="A1:B74"/>
   <sheetFormatPr defaultColWidth="8.72727272727273" defaultRowHeight="14" outlineLevelCol="1"/>
   <cols>
     <col min="2" max="2" width="198.454545454545" customWidth="1"/>
@@ -2204,6 +2210,14 @@
         <v>145</v>
       </c>
     </row>
+    <row r="74" spans="1:2">
+      <c r="A74" t="s">
+        <v>146</v>
+      </c>
+      <c r="B74" t="s">
+        <v>147</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
   <headerFooter/>
